--- a/data/ofm_1960_2024_components.xlsx
+++ b/data/ofm_1960_2024_components.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\POP\Pop_Estimates\2025\Final_Tables_for_Internet\working\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakaz\OneDrive\Desktop\Research\PopulationProjection\SubnationalPP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166678A8-9BD4-4532-80D1-CCB84113109C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC96110C-AF98-4B3D-9D9C-0BC23A71007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="660" windowWidth="27720" windowHeight="14625" tabRatio="682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11325" tabRatio="682" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="4" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="559">
   <si>
     <t>Adams</t>
   </si>
@@ -1759,7 +1759,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -2953,18 +2953,18 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
@@ -12280,7 +12280,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BP47"/>
+  <dimension ref="A1:BP45"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="3" bestFit="1" customWidth="1"/>
@@ -20788,11 +20788,6 @@
     <row r="45" spans="1:68" x14ac:dyDescent="0.2">
       <c r="BK45" s="5"/>
       <c r="BL45" s="5"/>
-    </row>
-    <row r="47" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="BK47" s="6" t="s">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
